--- a/output/laminas_comunales/comunal_o_ocup_a_2023_coquimbo.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2023_coquimbo.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,151 +375,151 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Andacollo</t>
         </is>
       </c>
       <c r="C2">
-        <v>37.9607797868456</v>
+        <v>59.3343343343343</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C3">
-        <v>36.730548195752</v>
+        <v>57.1754969917416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Andacollo</t>
+          <t>Illapel</t>
         </is>
       </c>
       <c r="C4">
-        <v>36.638686468038</v>
+        <v>56.9875022080904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4106</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vicuña</t>
+          <t>Salamanca</t>
         </is>
       </c>
       <c r="C5">
-        <v>36.1184578133731</v>
+        <v>56.7637492607924</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Salamanca</t>
+          <t>Ovalle</t>
         </is>
       </c>
       <c r="C6">
-        <v>35.6531593138213</v>
+        <v>55.2011264049717</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ovalle</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C7">
-        <v>35.3535834762578</v>
+        <v>55.1781929736263</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4201</t>
+          <t>4102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Illapel</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="C8">
-        <v>34.9764495232882</v>
+        <v>55.1159777679791</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Monte Patria</t>
+          <t>Vicuña</t>
         </is>
       </c>
       <c r="C9">
-        <v>33.3032029509514</v>
+        <v>54.0536662361888</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combarbalá</t>
+          <t>Monte Patria</t>
         </is>
       </c>
       <c r="C10">
-        <v>31.3366469312672</v>
+        <v>52.9689018464529</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Punitaqui</t>
+          <t>Combarbalá</t>
         </is>
       </c>
       <c r="C11">
-        <v>31.2022389532752</v>
+        <v>52.7704194260486</v>
       </c>
     </row>
     <row r="12">
@@ -534,52 +534,1417 @@
         </is>
       </c>
       <c r="C12">
-        <v>29.7002424509588</v>
+        <v>51.1461318051576</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Canela</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="C13">
-        <v>27.9930299302993</v>
+        <v>50.5159271530349</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>4203</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Los Vilos</t>
+          <t>Punitaqui</t>
         </is>
       </c>
       <c r="C14">
-        <v>27.2899049035096</v>
+        <v>49.8504345862964</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>47.8313840155945</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>47.7891763306571</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>47.6364484528067</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>47.6071861454075</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>47.0086207073538</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>46.5609476499809</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>46.5178972592482</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>46.135818617833</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>45.9569683876372</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>44.9109215706066</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>43.859603463777</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>43.676881812475</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>43.6478857011176</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>43.4858941760504</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>4104</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>La Higuera</t>
         </is>
       </c>
-      <c r="C15">
+      <c r="C29">
+        <v>43.3569611050527</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>43.3234043636549</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>43.0492099752522</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>42.6496748251148</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>42.2032267613973</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>41.0201179255076</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>41.01243339254</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>40.4942305850809</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>40.2996601791783</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>38.0578435478617</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>37.9607797868456</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>37.4002310438983</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>36.9071392910634</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>36.730548195752</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>36.638686468038</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>36.1184578133731</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>35.8966238740336</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>35.6978263860228</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>35.6531593138213</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>35.3535834762578</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>34.9764495232882</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>34.3397918909221</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>33.9114082741329</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>33.3032029509514</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>32.9258828094684</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>32.7816947382165</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>31.3722206805924</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>31.3366469312672</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>31.2022389532752</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>31.0426356589147</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>30.0576931783638</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>30.0096498483595</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>29.9654838893209</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>29.9438004917457</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>29.7992902090603</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>29.7037707278092</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>29.7002424509588</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>29.377148687554</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>29.3216273435202</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>29.250658613197</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>29.2482466393922</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>29.1925224945703</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>29.1806350504225</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>28.452380952381</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>28.3651885830785</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>27.9930299302993</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>27.8395276137548</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>27.7138157894737</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>27.6177521736811</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>27.2899049035096</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>27.2633744855967</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>26.8626498218335</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C81">
         <v>26.7918825561313</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>26.4800514800515</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>25.8626241609076</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>24.702380952381</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>24.5787014660867</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>24.0133382057373</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>23.9503426408919</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>23.7427794767244</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>21.8689108378687</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>21.1338607104079</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>4106</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Vicuña</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>12.5054324206867</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>La Serena</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>11.7659922684049</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>4103</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Andacollo</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>11.3141349500393</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>11.0155767008037</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>4102</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>10.8268873851545</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Monte Patria</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>10.4267757290078</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Ovalle</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>10.1966873706004</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Illapel</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>10.0986597170514</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>4204</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Salamanca</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>9.86391972023719</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>4304</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Punitaqui</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>9.23868938932846</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>4302</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Combarbalá</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>9.02810396117113</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>4305</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Río Hurtado</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>8.896620278330021</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Los Vilos</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>8.7501437277222</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>4202</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Canela</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>8.235261152208031</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>La Higuera</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>7.49354005167959</v>
       </c>
     </row>
   </sheetData>
